--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0002T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0002T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.57885440399104</v>
+        <v>7.894063840648545</v>
       </c>
       <c r="D2" t="n">
-        <v>44.75279320891602</v>
+        <v>7.272328896448855</v>
       </c>
       <c r="E2" t="n">
-        <v>6.364119853209125</v>
+        <v>1.034169476146483</v>
       </c>
       <c r="F2" t="n">
-        <v>17.03626640858321</v>
+        <v>2.768393291394772</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.84970195678619</v>
+        <v>9.725576567977756</v>
       </c>
       <c r="D3" t="n">
-        <v>43.64063517100676</v>
+        <v>7.091603215288599</v>
       </c>
       <c r="E3" t="n">
-        <v>6.364119853209125</v>
+        <v>1.034169476146483</v>
       </c>
       <c r="F3" t="n">
-        <v>17.03626640858321</v>
+        <v>2.768393291394772</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.88769824140315</v>
+        <v>7.294250964228012</v>
       </c>
       <c r="D4" t="n">
-        <v>8.07017259623797</v>
+        <v>1.31140304688867</v>
       </c>
       <c r="E4" t="n">
-        <v>6.364119853209125</v>
+        <v>1.034169476146483</v>
       </c>
       <c r="F4" t="n">
-        <v>17.03626640858321</v>
+        <v>2.768393291394772</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
